--- a/InputData/io-model/ACTR/Avg Corp Tax Rate.xlsx
+++ b/InputData/io-model/ACTR/Avg Corp Tax Rate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Dropbox (Energy Innovation)\My Documents\Energy Policy Solutions\US\Models\eps-us\InputData\io-model\ACTR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-india\InputData\io-model\ACTR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6361653D-74BA-485C-9BF1-04243361AEC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4E1F3C9-EBFB-4A61-8CFB-7FB198062DCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Source:</t>
   </si>
@@ -45,18 +45,6 @@
     <t>ACTR Average Corporate Tax Rate</t>
   </si>
   <si>
-    <t>Peter Peterson Foundation</t>
-  </si>
-  <si>
-    <t>The US Corporate Tax System Explained</t>
-  </si>
-  <si>
-    <t>https://www.pgpf.org/budget-basics/the-us-corporate-tax-system-explained</t>
-  </si>
-  <si>
-    <t>Combined federal and state corporate tax rate</t>
-  </si>
-  <si>
     <t>This is the average corporate tax rate paid, including national and subnational rates</t>
   </si>
   <si>
@@ -64,6 +52,15 @@
   </si>
   <si>
     <t>Tax Rate</t>
+  </si>
+  <si>
+    <t>Trading Economics</t>
+  </si>
+  <si>
+    <t>India Corporate Tax Rate</t>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/india/corporate-tax-rate#:~:text=The%20Corporate%20Tax%20Rate%20in,of%20Finance%2C%20Government%20of%20India</t>
   </si>
 </sst>
 </file>
@@ -429,49 +426,44 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" s="2">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -486,15 +478,15 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="45" customWidth="1"/>
-    <col min="2" max="2" width="26.21875" customWidth="1"/>
+    <col min="2" max="2" width="26.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B1">
         <v>2021</v>
@@ -587,128 +579,128 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B2">
-        <v>0.26</v>
+        <v>0.34939999999999999</v>
       </c>
       <c r="C2">
         <f>$B$2</f>
-        <v>0.26</v>
+        <v>0.34939999999999999</v>
       </c>
       <c r="D2">
         <f>$B$2</f>
-        <v>0.26</v>
+        <v>0.34939999999999999</v>
       </c>
       <c r="E2">
         <f t="shared" ref="E2:O2" si="0">$B$2</f>
-        <v>0.26</v>
+        <v>0.34939999999999999</v>
       </c>
       <c r="F2">
         <f t="shared" si="0"/>
-        <v>0.26</v>
+        <v>0.34939999999999999</v>
       </c>
       <c r="G2">
         <f t="shared" si="0"/>
-        <v>0.26</v>
+        <v>0.34939999999999999</v>
       </c>
       <c r="H2">
         <f t="shared" si="0"/>
-        <v>0.26</v>
+        <v>0.34939999999999999</v>
       </c>
       <c r="I2">
         <f t="shared" si="0"/>
-        <v>0.26</v>
+        <v>0.34939999999999999</v>
       </c>
       <c r="J2">
         <f t="shared" si="0"/>
-        <v>0.26</v>
+        <v>0.34939999999999999</v>
       </c>
       <c r="K2">
         <f t="shared" si="0"/>
-        <v>0.26</v>
+        <v>0.34939999999999999</v>
       </c>
       <c r="L2">
         <f t="shared" si="0"/>
-        <v>0.26</v>
+        <v>0.34939999999999999</v>
       </c>
       <c r="M2">
         <f t="shared" si="0"/>
-        <v>0.26</v>
+        <v>0.34939999999999999</v>
       </c>
       <c r="N2">
         <f t="shared" si="0"/>
-        <v>0.26</v>
+        <v>0.34939999999999999</v>
       </c>
       <c r="O2">
         <f t="shared" si="0"/>
-        <v>0.26</v>
+        <v>0.34939999999999999</v>
       </c>
       <c r="P2">
         <f>$B$2</f>
-        <v>0.26</v>
+        <v>0.34939999999999999</v>
       </c>
       <c r="Q2">
         <f>$B$2</f>
-        <v>0.26</v>
+        <v>0.34939999999999999</v>
       </c>
       <c r="R2">
         <f t="shared" ref="R2:V2" si="1">$B$2</f>
-        <v>0.26</v>
+        <v>0.34939999999999999</v>
       </c>
       <c r="S2">
         <f t="shared" si="1"/>
-        <v>0.26</v>
+        <v>0.34939999999999999</v>
       </c>
       <c r="T2">
         <f t="shared" si="1"/>
-        <v>0.26</v>
+        <v>0.34939999999999999</v>
       </c>
       <c r="U2">
         <f t="shared" si="1"/>
-        <v>0.26</v>
+        <v>0.34939999999999999</v>
       </c>
       <c r="V2">
         <f t="shared" si="1"/>
-        <v>0.26</v>
+        <v>0.34939999999999999</v>
       </c>
       <c r="W2">
         <f>$B$2</f>
-        <v>0.26</v>
+        <v>0.34939999999999999</v>
       </c>
       <c r="X2">
         <f>$B$2</f>
-        <v>0.26</v>
+        <v>0.34939999999999999</v>
       </c>
       <c r="Y2">
         <f t="shared" ref="Y2:AA2" si="2">$B$2</f>
-        <v>0.26</v>
+        <v>0.34939999999999999</v>
       </c>
       <c r="Z2">
         <f t="shared" si="2"/>
-        <v>0.26</v>
+        <v>0.34939999999999999</v>
       </c>
       <c r="AA2">
         <f t="shared" si="2"/>
-        <v>0.26</v>
+        <v>0.34939999999999999</v>
       </c>
       <c r="AB2">
         <f>$B$2</f>
-        <v>0.26</v>
+        <v>0.34939999999999999</v>
       </c>
       <c r="AC2">
         <f>$B$2</f>
-        <v>0.26</v>
+        <v>0.34939999999999999</v>
       </c>
       <c r="AD2">
-        <f t="shared" ref="AD2:AM2" si="3">$B$2</f>
-        <v>0.26</v>
+        <f t="shared" ref="AD2:AE2" si="3">$B$2</f>
+        <v>0.34939999999999999</v>
       </c>
       <c r="AE2">
         <f t="shared" si="3"/>
-        <v>0.26</v>
+        <v>0.34939999999999999</v>
       </c>
     </row>
   </sheetData>
